--- a/numerical-workflows/v2/framework/04_数值文档/节奏/全玩法难度线_数值文档.xlsx
+++ b/numerical-workflows/v2/framework/04_数值文档/节奏/全玩法难度线_数值文档.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="覆盖状态" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="主线" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="困难主线" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="资源副本-金币" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="资源副本-角色经验" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="资源副本-专武经验" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="旅券副本" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="映射装备副本" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="大秘境" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="无限挑战" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="爬塔" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="竞技场(PVPVE)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="BOSS挑战" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖状态" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主线" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="困难主线" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源副本-金币" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源副本-角色经验" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源副本-专武经验" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旅券副本" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="映射装备副本" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大秘境" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="无限挑战" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="爬塔" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞技场(PVPVE)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOSS挑战" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
